--- a/docs/alliance-templates/alliance-agreements.xlsx
+++ b/docs/alliance-templates/alliance-agreements.xlsx
@@ -7,27 +7,19 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="合作协议" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'合作协议'!$A$2:$F$2</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$F$6</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>填写说明：
-* 必填列。
-协议类型：文本，选填
-开始日期 / 结束日期：格式 YYYY-MM-DD，选填
-状态：draft（草稿）/ active（有效）/ expired（失效），默认为 draft
-内容：文本，选填</t>
-  </si>
-  <si>
-    <t>协议名称 *</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>协议名称</t>
   </si>
   <si>
     <t>协议类型</t>
@@ -43,13 +35,97 @@
   </si>
   <si>
     <t>内容</t>
+  </si>
+  <si>
+    <t>华为-校企合作框架协议</t>
+  </si>
+  <si>
+    <t>战略合作</t>
+  </si>
+  <si>
+    <t>2026-01-01</t>
+  </si>
+  <si>
+    <t>2029-12-31</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>共建人工智能实验室，联合培养研究生，互派师资</t>
+  </si>
+  <si>
+    <t>阿里巴巴-产教融合协议</t>
+  </si>
+  <si>
+    <t>人才培养</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2028-02-28</t>
+  </si>
+  <si>
+    <t>联合开展电子商务与大数据方向人才培养</t>
+  </si>
+  <si>
+    <t>比亚迪-实训基地协议</t>
+  </si>
+  <si>
+    <t>实训基地</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>2028-08-31</t>
+  </si>
+  <si>
+    <t>建设新能源汽车实训基地，提供实习岗位30个/年</t>
+  </si>
+  <si>
+    <t>腾讯-课程共建协议</t>
+  </si>
+  <si>
+    <t>课程共建</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>2027-05-31</t>
+  </si>
+  <si>
+    <t>draft</t>
+  </si>
+  <si>
+    <t>联合开发云计算与人工智能方向课程</t>
+  </si>
+  <si>
+    <t>中兴-技术合作备忘录</t>
+  </si>
+  <si>
+    <t>技术研发</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2027-01-14</t>
+  </si>
+  <si>
+    <t>expired</t>
+  </si>
+  <si>
+    <t>5G通信技术联合研究，已到期待续签</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,14 +135,8 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
       <sz val="11"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,7 +148,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,34 +160,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -384,52 +438,140 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="true"/>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="28"/>
-    <col customWidth="true" max="2" min="2" width="22"/>
-    <col customWidth="true" max="4" min="3" width="16"/>
-    <col customWidth="true" max="5" min="5" width="20"/>
-    <col customWidth="true" max="6" min="6" width="48"/>
+    <col customWidth="true" max="2" min="2" width="18"/>
+    <col customWidth="true" max="4" min="3" width="14"/>
+    <col customWidth="true" max="5" min="5" width="12"/>
+    <col customWidth="true" max="6" min="6" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" ht="112" customHeight="true">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="24" customHeight="true">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="true">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="2" ht="20" customHeight="true">
+      <c r="A2" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$2:$F$2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
+  <autoFilter ref="$A$1:$F$6"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-agreements.xlsx
+++ b/docs/alliance-templates/alliance-agreements.xlsx
@@ -1,131 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合作协议" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'合作协议'!$A$2:$F$2</definedName>
   </definedNames>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
-  <si>
-    <t>协议名称</t>
-  </si>
-  <si>
-    <t>协议类型</t>
-  </si>
-  <si>
-    <t>开始日期</t>
-  </si>
-  <si>
-    <t>结束日期</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>内容</t>
-  </si>
-  <si>
-    <t>华为-校企合作框架协议</t>
-  </si>
-  <si>
-    <t>战略合作</t>
-  </si>
-  <si>
-    <t>2026-01-01</t>
-  </si>
-  <si>
-    <t>2029-12-31</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>共建人工智能实验室，联合培养研究生，互派师资</t>
-  </si>
-  <si>
-    <t>阿里巴巴-产教融合协议</t>
-  </si>
-  <si>
-    <t>人才培养</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>2028-02-28</t>
-  </si>
-  <si>
-    <t>联合开展电子商务与大数据方向人才培养</t>
-  </si>
-  <si>
-    <t>比亚迪-实训基地协议</t>
-  </si>
-  <si>
-    <t>实训基地</t>
-  </si>
-  <si>
-    <t>2025-09-01</t>
-  </si>
-  <si>
-    <t>2028-08-31</t>
-  </si>
-  <si>
-    <t>建设新能源汽车实训基地，提供实习岗位30个/年</t>
-  </si>
-  <si>
-    <t>腾讯-课程共建协议</t>
-  </si>
-  <si>
-    <t>课程共建</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>2027-05-31</t>
-  </si>
-  <si>
-    <t>draft</t>
-  </si>
-  <si>
-    <t>联合开发云计算与人工智能方向课程</t>
-  </si>
-  <si>
-    <t>中兴-技术合作备忘录</t>
-  </si>
-  <si>
-    <t>技术研发</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2027-01-14</t>
-  </si>
-  <si>
-    <t>expired</t>
-  </si>
-  <si>
-    <t>5G通信技术联合研究，已到期待续签</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -135,13 +28,23 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -151,8 +54,20 @@
         <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -161,24 +76,113 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -439,139 +443,236 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="true"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="28"/>
-    <col customWidth="true" max="2" min="2" width="18"/>
-    <col customWidth="true" max="4" min="3" width="14"/>
-    <col customWidth="true" max="5" min="5" width="12"/>
-    <col customWidth="true" max="6" min="6" width="50"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="true">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
+    <row r="1" ht="128" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>填写说明：
+* 必填列。
+协议类型：文本，选填
+开始日期 / 结束日期：格式 YYYY-MM-DD，选填
+状态：draft（草稿）/ active（有效）/ expired（失效），默认为 draft
+内容：文本，选填</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
     </row>
-    <row r="2" ht="20" customHeight="true">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>协议名称 *</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>协议类型</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>开始日期</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>结束日期</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="true">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>华为-校企合作框架协议</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>战略合作</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>2029-12-31</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>共建人工智能实验室，联合培养研究生，互派师资</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="true">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>阿里巴巴-产教融合协议</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>人才培养</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>2028-02-28</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>联合开展电子商务与大数据方向人才培养</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="true">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>27</v>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>比亚迪-实训基地协议</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>实训基地</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>2028-08-31</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>建设新能源汽车实训基地，提供实习岗位30个/年</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="true">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>33</v>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>腾讯-课程共建协议</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>课程共建</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>2027-05-31</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>draft</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>联合开发云计算与人工智能方向课程</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>中兴-技术合作备忘录</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>技术研发</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>2027-01-14</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>expired</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>5G通信技术联合研究，已到期待续签</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$F$6"/>
+  <autoFilter ref="A2:F2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-agreements.xlsx
+++ b/docs/alliance-templates/alliance-agreements.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合作协议" sheetId="1" state="visible" r:id="rId1"/>
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -90,11 +90,55 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,6 +154,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,11 +516,11 @@
 内容：文本，选填</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="8" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -531,7 +577,7 @@
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>生效中</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
@@ -563,7 +609,7 @@
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>生效中</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
@@ -595,7 +641,7 @@
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>生效中</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -627,7 +673,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>草稿</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -659,7 +705,7 @@
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>expired</t>
+          <t>已失效</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
